--- a/tasks/finalpool/12306-yf-investor-roadshow-excel-ppt-email/groundtruth_workspace/Roadshow_Analysis.xlsx
+++ b/tasks/finalpool/12306-yf-investor-roadshow-excel-ppt-email/groundtruth_workspace/Roadshow_Analysis.xlsx
@@ -595,28 +595,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apple Inc</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AAPL</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>185.5</v>
+        <v>300.88</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.3</v>
+        <v>-11.4</v>
       </c>
       <c r="E2" t="n">
-        <v>2850</v>
+        <v>3639.7</v>
       </c>
       <c r="F2" t="n">
-        <v>394.3</v>
+        <v>402.8</v>
       </c>
       <c r="G2" t="n">
-        <v>6.16</v>
+        <v>10.82</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -627,28 +627,28 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Microsoft Corp</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>378.9</v>
+        <v>218.94</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>2820</v>
+        <v>2350.3</v>
       </c>
       <c r="F3" t="n">
-        <v>211.9</v>
+        <v>716.9</v>
       </c>
       <c r="G3" t="n">
-        <v>11.45</v>
+        <v>7.18</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -694,23 +694,23 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>394.3</v>
+        <v>402.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Net_Income</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="n">
-        <v>99.8</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="4">
@@ -720,23 +720,23 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C4" t="n">
-        <v>365.8</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Net_Income</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>99.8</v>
+        <v>100.1</v>
       </c>
     </row>
   </sheetData>
